--- a/rapporten/prijsrapport-2026-05-05.xlsx
+++ b/rapporten/prijsrapport-2026-05-05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="152">
   <si>
     <t>Product</t>
   </si>
@@ -37,148 +37,274 @@
     <t>Fulfilment</t>
   </si>
   <si>
+    <t>Creation Lamis Just Perfect Dream for her - Eau de parfum met bloemige noten - 100ml</t>
+  </si>
+  <si>
     <t>5414666014427</t>
   </si>
   <si>
-    <t>1692530</t>
+    <t>Juwelium</t>
   </si>
   <si>
     <t>FBR</t>
   </si>
   <si>
+    <t>NG Dark Elixir Men Eau de Toilette 100 ml</t>
+  </si>
+  <si>
     <t>8719214757229</t>
   </si>
   <si>
-    <t>1556816</t>
+    <t>Dorsh</t>
+  </si>
+  <si>
+    <t>Omerta Love Feathers - Eau de parfum - 100ML</t>
   </si>
   <si>
     <t>8715658999430</t>
   </si>
   <si>
-    <t>1840300</t>
+    <t>Bliksma Retail B.V.</t>
+  </si>
+  <si>
+    <t>Omerta - Pink Shoe - Eau de Parfum 100ml</t>
   </si>
   <si>
     <t>8715658380931</t>
   </si>
   <si>
+    <t>Omerta - Big Release The Mood - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658370086</t>
   </si>
   <si>
+    <t>Omerta - Golden challenge EDT men 100 ml</t>
+  </si>
+  <si>
     <t>8720938379345</t>
   </si>
   <si>
+    <t>Omerta - Invasion - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
     <t>8715658380351</t>
   </si>
   <si>
+    <t>Omerta - L'uomo X - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370505</t>
   </si>
   <si>
+    <t>Omerta - Oh So Black For Women - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380221</t>
   </si>
   <si>
+    <t>Omerta - Twice so nice - Eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8720938379352</t>
   </si>
   <si>
+    <t>Omerta - Royal X Red - EDT men 100ml</t>
+  </si>
+  <si>
     <t>8715658370369</t>
   </si>
   <si>
+    <t>Omerta Clouds of Love Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658999638</t>
   </si>
   <si>
+    <t>Omerta - Conclude Oud Extreme Attraction - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658370543</t>
   </si>
   <si>
+    <t>Omerta -Ladies World- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380757</t>
   </si>
   <si>
+    <t>Omerta -Lazy Nights- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380405</t>
   </si>
   <si>
+    <t>Omerta -Shoe Red- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380672</t>
   </si>
   <si>
+    <t>Omerta - Sensible Man - EDT men - 100ml</t>
+  </si>
+  <si>
     <t>8715658999249</t>
   </si>
   <si>
+    <t>Omerta - Love Dust - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380115</t>
   </si>
   <si>
+    <t>Omerta - Express Sensualite Energy - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658998839</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Ladies World - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658997993</t>
   </si>
   <si>
+    <t>Omerta -Shoe Blue- Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658380665</t>
   </si>
   <si>
+    <t>Omerta - Golden Challenge Elixer - 1EDT men 100ml</t>
+  </si>
+  <si>
     <t>8715658370437</t>
   </si>
   <si>
+    <t>Omerta Invasion Awakening - Vrouwelijke eau de parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380658</t>
   </si>
   <si>
+    <t>Omerta Meet Me On The Wild Site Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658370062</t>
   </si>
   <si>
+    <t>Omerta - La Donna X - Eau De Parfum - for women - 100ML</t>
+  </si>
+  <si>
     <t>8715658380580</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Lovely Lily - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494225</t>
   </si>
   <si>
-    <t>946246</t>
+    <t>Minimarkt W&amp;M</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Like a Fairytale - Glimmering Grace - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
   </si>
   <si>
     <t>8721055494263</t>
   </si>
   <si>
+    <t>Hello Kitty-Cotton Candy- suikerspin - 15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816691</t>
   </si>
   <si>
+    <t>Hello Kitty-Peach-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816677</t>
   </si>
   <si>
+    <t>Hello Kitty-Vanilla-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816653</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Magical Mae - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494270</t>
   </si>
   <si>
+    <t>Bubble Bliss - Like a Fairytale - Dreamy Daisy - Eau de Parfum - Prinsessen Voor Kinderen 15ml</t>
+  </si>
+  <si>
     <t>8721055494232</t>
   </si>
   <si>
+    <t>Hello Kitty-Apple-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816714</t>
   </si>
   <si>
+    <t>Hello Kitty-Coconut-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816615</t>
   </si>
   <si>
+    <t>Hello Kitty-Rainbow-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493211</t>
   </si>
   <si>
+    <t>Hello Kitty-Girl Gang-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816790</t>
   </si>
   <si>
+    <t>Hello Kitty-Strawberry-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816639</t>
   </si>
   <si>
+    <t>Hello Kitty-Spring Time-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816837</t>
   </si>
   <si>
+    <t>Hello Kitty-I feel so pretty today!-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>7640158816813</t>
   </si>
   <si>
+    <t>Hello Kitty-Best Friend-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493198</t>
   </si>
   <si>
+    <t>Hello Kitty-You Are Cute-15ml Eau de Parfum</t>
+  </si>
+  <si>
     <t>8721055493228</t>
   </si>
   <si>
+    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>7640158817018</t>
   </si>
   <si>
-    <t>1762224</t>
+    <t>Koopjesfun.nl</t>
   </si>
   <si>
     <t>NG Axure Sport Eau de Toilette 100ml</t>
@@ -193,9 +319,15 @@
     <t>8721055493747</t>
   </si>
   <si>
+    <t>Omerta - Big The Fragrance Release - Eau De Toilette - 100ML</t>
+  </si>
+  <si>
     <t>8715658370093</t>
   </si>
   <si>
+    <t>Omerta - Out Of Question - Eau de parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658380412</t>
   </si>
   <si>
@@ -205,6 +337,9 @@
     <t>5414666009485</t>
   </si>
   <si>
+    <t>Bubble Bliss - Giftset - Unicorn Cherry Blossom Fantasy - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
     <t>8721055494065</t>
   </si>
   <si>
@@ -238,30 +373,57 @@
     <t>8719214752699</t>
   </si>
   <si>
+    <t>Sentio Inter Feer men Eau de toilette spray for him 100ml</t>
+  </si>
+  <si>
     <t>7640158815021</t>
   </si>
   <si>
+    <t>Real Time - Blooming Flower Nectar - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
     <t>8715658361435</t>
   </si>
   <si>
+    <t>Real Time Wild Action Elixir men edt 100 ml</t>
+  </si>
+  <si>
     <t>8715658350637</t>
   </si>
   <si>
+    <t>Real Time Canyon night 100 ml eau de toilette spray</t>
+  </si>
+  <si>
     <t>8715658002796</t>
   </si>
   <si>
+    <t>Real Time - Tempting Rumors - Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658361619</t>
   </si>
   <si>
+    <t>Vibezz Blissful Life parfum - Eau de parfum voor haar - 100ml</t>
+  </si>
+  <si>
     <t>7640158819180</t>
   </si>
   <si>
+    <t>Omerta Hatch Eau de Toilette 100ml</t>
+  </si>
+  <si>
     <t>8715658997702</t>
   </si>
   <si>
+    <t>Omerta - Rose Pure - Eau de Parfum - 100ml</t>
+  </si>
+  <si>
     <t>8715658380696</t>
   </si>
   <si>
+    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
+  </si>
+  <si>
     <t>8715658350705</t>
   </si>
   <si>
@@ -271,9 +433,15 @@
     <t>8721055492146</t>
   </si>
   <si>
+    <t>Dorall Everscent Eau de Toilette voor dames - 100ml</t>
+  </si>
+  <si>
     <t>6291012875807</t>
   </si>
   <si>
+    <t>Creation Lamis Golden Wave Women Giftset</t>
+  </si>
+  <si>
     <t>6291012002623</t>
   </si>
   <si>
@@ -289,7 +457,13 @@
     <t>7640158815694</t>
   </si>
   <si>
+    <t>Street Looks Miss Important Eau de Parfum 100ml</t>
+  </si>
+  <si>
     <t>8715658340287</t>
+  </si>
+  <si>
+    <t>Sentio Soft Suede Eau de Parfum 100ml</t>
   </si>
   <si>
     <t>8721055491453</t>
@@ -728,7 +902,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1">
         <v>9.95</v>
@@ -740,21 +914,21 @@
         <v>0.47</v>
       </c>
       <c r="F2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1">
         <v>9.48</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C3" s="1">
         <v>9.79</v>
@@ -766,21 +940,21 @@
         <v>0.3</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G3" s="1">
         <v>9.49</v>
       </c>
       <c r="H3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="1">
         <v>9.79</v>
@@ -792,21 +966,21 @@
         <v>0.29</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1">
         <v>9.5</v>
       </c>
       <c r="H4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C5" s="1">
         <v>9.79</v>
@@ -818,21 +992,21 @@
         <v>0.29</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G5" s="1">
         <v>9.5</v>
       </c>
       <c r="H5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>9.79</v>
@@ -844,21 +1018,21 @@
         <v>0.29</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1">
         <v>9.5</v>
       </c>
       <c r="H6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
         <v>9.79</v>
@@ -870,21 +1044,21 @@
         <v>0.29</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G7" s="1">
         <v>9.5</v>
       </c>
       <c r="H7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1">
         <v>9.79</v>
@@ -896,21 +1070,21 @@
         <v>0.29</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G8" s="1">
         <v>9.5</v>
       </c>
       <c r="H8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1">
         <v>9.79</v>
@@ -922,21 +1096,21 @@
         <v>0.29</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G9" s="1">
         <v>9.5</v>
       </c>
       <c r="H9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1">
         <v>9.79</v>
@@ -948,21 +1122,21 @@
         <v>0.29</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G10" s="1">
         <v>9.5</v>
       </c>
       <c r="H10" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1">
         <v>9.79</v>
@@ -974,21 +1148,21 @@
         <v>0.29</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1">
         <v>9.5</v>
       </c>
       <c r="H11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C12" s="1">
         <v>9.79</v>
@@ -1000,21 +1174,21 @@
         <v>0.29</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G12" s="1">
         <v>9.5</v>
       </c>
       <c r="H12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>9.79</v>
@@ -1026,21 +1200,21 @@
         <v>0.29</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G13" s="1">
         <v>9.5</v>
       </c>
       <c r="H13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C14" s="1">
         <v>9.79</v>
@@ -1052,21 +1226,21 @@
         <v>0.29</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G14" s="1">
         <v>9.5</v>
       </c>
       <c r="H14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1">
         <v>9.79</v>
@@ -1078,21 +1252,21 @@
         <v>0.29</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G15" s="1">
         <v>9.5</v>
       </c>
       <c r="H15" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="C16" s="1">
         <v>9.79</v>
@@ -1104,21 +1278,21 @@
         <v>0.29</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G16" s="1">
         <v>9.5</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C17" s="1">
         <v>9.79</v>
@@ -1130,21 +1304,21 @@
         <v>0.29</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G17" s="1">
         <v>9.5</v>
       </c>
       <c r="H17" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1">
         <v>9.79</v>
@@ -1156,21 +1330,21 @@
         <v>0.29</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G18" s="1">
         <v>9.5</v>
       </c>
       <c r="H18" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C19" s="1">
         <v>9.79</v>
@@ -1182,21 +1356,21 @@
         <v>0.29</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
         <v>9.5</v>
       </c>
       <c r="H19" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1">
         <v>9.79</v>
@@ -1208,21 +1382,21 @@
         <v>0.29</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G20" s="1">
         <v>9.5</v>
       </c>
       <c r="H20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C21" s="1">
         <v>9.79</v>
@@ -1234,21 +1408,21 @@
         <v>0.29</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G21" s="1">
         <v>9.5</v>
       </c>
       <c r="H21" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1">
         <v>9.79</v>
@@ -1260,21 +1434,21 @@
         <v>0.29</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G22" s="1">
         <v>9.5</v>
       </c>
       <c r="H22" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C23" s="1">
         <v>9.79</v>
@@ -1286,21 +1460,21 @@
         <v>0.29</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G23" s="1">
         <v>9.5</v>
       </c>
       <c r="H23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C24" s="1">
         <v>9.79</v>
@@ -1312,21 +1486,21 @@
         <v>0.29</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G24" s="1">
         <v>9.5</v>
       </c>
       <c r="H24" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B25" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C25" s="1">
         <v>9.79</v>
@@ -1338,21 +1512,21 @@
         <v>0.29</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G25" s="1">
         <v>9.5</v>
       </c>
       <c r="H25" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C26" s="1">
         <v>9.79</v>
@@ -1364,21 +1538,21 @@
         <v>0.29</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G26" s="1">
         <v>9.5</v>
       </c>
       <c r="H26" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C27" s="1">
         <v>5.25</v>
@@ -1390,21 +1564,21 @@
         <v>0.26</v>
       </c>
       <c r="F27" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G27" s="1">
         <v>4.99</v>
       </c>
       <c r="H27" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C28" s="1">
         <v>5.25</v>
@@ -1416,21 +1590,21 @@
         <v>0.26</v>
       </c>
       <c r="F28" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G28" s="1">
         <v>4.99</v>
       </c>
       <c r="H28" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="C29" s="1">
         <v>5.25</v>
@@ -1442,21 +1616,21 @@
         <v>0.26</v>
       </c>
       <c r="F29" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G29" s="1">
         <v>4.99</v>
       </c>
       <c r="H29" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
         <v>5.25</v>
@@ -1468,21 +1642,21 @@
         <v>0.26</v>
       </c>
       <c r="F30" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G30" s="1">
         <v>4.99</v>
       </c>
       <c r="H30" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>5.25</v>
@@ -1494,21 +1668,21 @@
         <v>0.26</v>
       </c>
       <c r="F31" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G31" s="1">
         <v>4.99</v>
       </c>
       <c r="H31" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C32" s="1">
         <v>5.25</v>
@@ -1520,21 +1694,21 @@
         <v>0.26</v>
       </c>
       <c r="F32" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G32" s="1">
         <v>4.99</v>
       </c>
       <c r="H32" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="B33" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C33" s="1">
         <v>5.25</v>
@@ -1546,21 +1720,21 @@
         <v>0.26</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G33" s="1">
         <v>4.99</v>
       </c>
       <c r="H33" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="B34" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>5.25</v>
@@ -1572,21 +1746,21 @@
         <v>0.26</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G34" s="1">
         <v>4.99</v>
       </c>
       <c r="H34" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="C35" s="1">
         <v>5.25</v>
@@ -1598,21 +1772,21 @@
         <v>0.26</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G35" s="1">
         <v>4.99</v>
       </c>
       <c r="H35" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C36" s="1">
         <v>5.25</v>
@@ -1624,21 +1798,21 @@
         <v>0.26</v>
       </c>
       <c r="F36" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G36" s="1">
         <v>4.99</v>
       </c>
       <c r="H36" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>48</v>
+        <v>83</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1">
         <v>5.25</v>
@@ -1650,21 +1824,21 @@
         <v>0.26</v>
       </c>
       <c r="F37" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G37" s="1">
         <v>4.99</v>
       </c>
       <c r="H37" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="B38" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="C38" s="1">
         <v>5.25</v>
@@ -1676,21 +1850,21 @@
         <v>0.26</v>
       </c>
       <c r="F38" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G38" s="1">
         <v>4.99</v>
       </c>
       <c r="H38" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="C39" s="1">
         <v>5.25</v>
@@ -1702,21 +1876,21 @@
         <v>0.26</v>
       </c>
       <c r="F39" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G39" s="1">
         <v>4.99</v>
       </c>
       <c r="H39" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="B40" t="s">
-        <v>51</v>
+        <v>90</v>
       </c>
       <c r="C40" s="1">
         <v>5.25</v>
@@ -1728,21 +1902,21 @@
         <v>0.26</v>
       </c>
       <c r="F40" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G40" s="1">
         <v>4.99</v>
       </c>
       <c r="H40" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C41" s="1">
         <v>5.25</v>
@@ -1754,21 +1928,21 @@
         <v>0.26</v>
       </c>
       <c r="F41" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G41" s="1">
         <v>4.99</v>
       </c>
       <c r="H41" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
       <c r="C42" s="1">
         <v>5.25</v>
@@ -1780,21 +1954,21 @@
         <v>0.26</v>
       </c>
       <c r="F42" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="G42" s="1">
         <v>4.99</v>
       </c>
       <c r="H42" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>95</v>
       </c>
       <c r="B43" t="s">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="C43" s="1">
         <v>15.55</v>
@@ -1806,21 +1980,21 @@
         <v>0.18</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G43" s="1">
         <v>15.37</v>
       </c>
       <c r="H43" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>98</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="C44" s="1">
         <v>14.95</v>
@@ -1832,21 +2006,21 @@
         <v>0.17</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G44" s="1">
         <v>14.78</v>
       </c>
       <c r="H44" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="C45" s="1">
         <v>14.95</v>
@@ -1858,21 +2032,21 @@
         <v>0.17</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G45" s="1">
         <v>14.78</v>
       </c>
       <c r="H45" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1">
         <v>14.95</v>
@@ -1884,21 +2058,21 @@
         <v>0.17</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G46" s="1">
         <v>14.78</v>
       </c>
       <c r="H46" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C47" s="1">
         <v>14.19</v>
@@ -1910,21 +2084,21 @@
         <v>0.12</v>
       </c>
       <c r="F47" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G47" s="1">
         <v>14.07</v>
       </c>
       <c r="H47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C48" s="1">
         <v>14.89</v>
@@ -1936,21 +2110,21 @@
         <v>0.11</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G48" s="1">
         <v>14.78</v>
       </c>
       <c r="H48" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>109</v>
       </c>
       <c r="C49" s="1">
         <v>14.89</v>
@@ -1962,21 +2136,21 @@
         <v>0.11</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G49" s="1">
         <v>14.78</v>
       </c>
       <c r="H49" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>111</v>
       </c>
       <c r="C50" s="1">
         <v>14.29</v>
@@ -1988,21 +2162,21 @@
         <v>0.09</v>
       </c>
       <c r="F50" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G50" s="1">
         <v>14.2</v>
       </c>
       <c r="H50" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>67</v>
+        <v>112</v>
       </c>
       <c r="B51" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1">
         <v>14.29</v>
@@ -2014,21 +2188,21 @@
         <v>0.09</v>
       </c>
       <c r="F51" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G51" s="1">
         <v>14.2</v>
       </c>
       <c r="H51" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1">
         <v>14.29</v>
@@ -2040,21 +2214,21 @@
         <v>0.09</v>
       </c>
       <c r="F52" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G52" s="1">
         <v>14.2</v>
       </c>
       <c r="H52" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="B53" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="C53" s="1">
         <v>14.29</v>
@@ -2066,21 +2240,21 @@
         <v>0.09</v>
       </c>
       <c r="F53" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G53" s="1">
         <v>14.2</v>
       </c>
       <c r="H53" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="C54" s="1">
         <v>14.29</v>
@@ -2092,21 +2266,21 @@
         <v>0.09</v>
       </c>
       <c r="F54" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G54" s="1">
         <v>14.2</v>
       </c>
       <c r="H54" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="C55" s="1">
         <v>14.29</v>
@@ -2118,21 +2292,21 @@
         <v>0.09</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G55" s="1">
         <v>14.2</v>
       </c>
       <c r="H55" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>76</v>
+        <v>122</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>123</v>
       </c>
       <c r="C56" s="1">
         <v>14.29</v>
@@ -2144,21 +2318,21 @@
         <v>0.09</v>
       </c>
       <c r="F56" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G56" s="1">
         <v>14.2</v>
       </c>
       <c r="H56" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
+        <v>125</v>
       </c>
       <c r="C57" s="1">
         <v>14.29</v>
@@ -2170,21 +2344,21 @@
         <v>0.09</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G57" s="1">
         <v>14.2</v>
       </c>
       <c r="H57" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>127</v>
       </c>
       <c r="C58" s="1">
         <v>14.29</v>
@@ -2196,21 +2370,21 @@
         <v>0.09</v>
       </c>
       <c r="F58" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G58" s="1">
         <v>14.2</v>
       </c>
       <c r="H58" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="B59" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C59" s="1">
         <v>14.29</v>
@@ -2222,21 +2396,21 @@
         <v>0.09</v>
       </c>
       <c r="F59" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G59" s="1">
         <v>14.2</v>
       </c>
       <c r="H59" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="B60" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C60" s="1">
         <v>14.29</v>
@@ -2248,21 +2422,21 @@
         <v>0.09</v>
       </c>
       <c r="F60" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G60" s="1">
         <v>14.2</v>
       </c>
       <c r="H60" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>133</v>
       </c>
       <c r="C61" s="1">
         <v>14.29</v>
@@ -2274,21 +2448,21 @@
         <v>0.09</v>
       </c>
       <c r="F61" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G61" s="1">
         <v>14.2</v>
       </c>
       <c r="H61" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="C62" s="1">
         <v>14.29</v>
@@ -2300,21 +2474,21 @@
         <v>0.09</v>
       </c>
       <c r="F62" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G62" s="1">
         <v>14.2</v>
       </c>
       <c r="H62" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="B63" t="s">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="C63" s="1">
         <v>14.29</v>
@@ -2326,21 +2500,21 @@
         <v>0.09</v>
       </c>
       <c r="F63" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G63" s="1">
         <v>14.2</v>
       </c>
       <c r="H63" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="B64" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="C64" s="1">
         <v>15.59</v>
@@ -2352,21 +2526,21 @@
         <v>0.08</v>
       </c>
       <c r="F64" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G64" s="1">
         <v>15.51</v>
       </c>
       <c r="H64" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="C65" s="1">
         <v>13.89</v>
@@ -2378,21 +2552,21 @@
         <v>0.07</v>
       </c>
       <c r="F65" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G65" s="1">
         <v>13.82</v>
       </c>
       <c r="H65" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="C66" s="1">
         <v>13.49</v>
@@ -2404,21 +2578,21 @@
         <v>0.06</v>
       </c>
       <c r="F66" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G66" s="1">
         <v>13.43</v>
       </c>
       <c r="H66" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>88</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="C67" s="1">
         <v>13.75</v>
@@ -2430,21 +2604,21 @@
         <v>0.05</v>
       </c>
       <c r="F67" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G67" s="1">
         <v>13.7</v>
       </c>
       <c r="H67" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="C68" s="1">
         <v>12.69</v>
@@ -2456,21 +2630,21 @@
         <v>0.03</v>
       </c>
       <c r="F68" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G68" s="1">
         <v>12.66</v>
       </c>
       <c r="H68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C69" s="1">
         <v>12.99</v>
@@ -2482,21 +2656,21 @@
         <v>0.03</v>
       </c>
       <c r="F69" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G69" s="1">
         <v>12.96</v>
       </c>
       <c r="H69" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>93</v>
+        <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>151</v>
       </c>
       <c r="C70" s="1">
         <v>14.79</v>
@@ -2508,13 +2682,13 @@
         <v>0.01</v>
       </c>
       <c r="F70" t="s">
-        <v>55</v>
+        <v>97</v>
       </c>
       <c r="G70" s="1">
         <v>14.78</v>
       </c>
       <c r="H70" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/rapporten/prijsrapport-2026-05-05.xlsx
+++ b/rapporten/prijsrapport-2026-05-05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
   <si>
     <t>Product</t>
   </si>
@@ -298,175 +298,67 @@
     <t>8721055493228</t>
   </si>
   <si>
-    <t>Hello Kitty - Giftset - Sweet Leopard - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>7640158817018</t>
+    <t>Atelier Privee Mistical France Unisex - Sugar Fortune - Eau de Parfum - 100ml</t>
+  </si>
+  <si>
+    <t>8721055495765</t>
   </si>
   <si>
     <t>Koopjesfun.nl</t>
   </si>
   <si>
-    <t>NG Axure Sport Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8719214758325</t>
-  </si>
-  <si>
-    <t>Sentio Love &amp; Casual for Everyone Eau de Parfum Spray 100 ml</t>
-  </si>
-  <si>
-    <t>8721055493747</t>
-  </si>
-  <si>
-    <t>Omerta - Big The Fragrance Release - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658370093</t>
-  </si>
-  <si>
-    <t>Omerta - Out Of Question - Eau de parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658380412</t>
-  </si>
-  <si>
-    <t>Creation Lamis - Golden Wave for him - Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>5414666009485</t>
-  </si>
-  <si>
-    <t>Bubble Bliss - Giftset - Unicorn Cherry Blossom Fantasy - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
-  </si>
-  <si>
-    <t>8721055494065</t>
-  </si>
-  <si>
-    <t>Real Time - Intense Impression For Men - Eau De Toilette - 100ML</t>
-  </si>
-  <si>
-    <t>8715658350361</t>
-  </si>
-  <si>
-    <t>Omerta Pure E-motion Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658997436</t>
-  </si>
-  <si>
-    <t>Omerta Liquid Marble Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658370147</t>
-  </si>
-  <si>
-    <t>Omerta - Laverder Fields - Eau de Parfum - 100ml</t>
-  </si>
-  <si>
-    <t>8715658380702</t>
-  </si>
-  <si>
-    <t>Next Generation Touch Desire Eau de Parfum 80ml</t>
-  </si>
-  <si>
-    <t>8719214752699</t>
-  </si>
-  <si>
-    <t>Sentio Inter Feer men Eau de toilette spray for him 100ml</t>
-  </si>
-  <si>
-    <t>7640158815021</t>
-  </si>
-  <si>
-    <t>Real Time - Blooming Flower Nectar - Eau De Parfum - 100ML</t>
-  </si>
-  <si>
-    <t>8715658361435</t>
-  </si>
-  <si>
-    <t>Real Time Wild Action Elixir men edt 100 ml</t>
-  </si>
-  <si>
-    <t>8715658350637</t>
-  </si>
-  <si>
-    <t>Real Time Canyon night 100 ml eau de toilette spray</t>
-  </si>
-  <si>
-    <t>8715658002796</t>
-  </si>
-  <si>
-    <t>Real Time - Tempting Rumors - Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658361619</t>
-  </si>
-  <si>
-    <t>Vibezz Blissful Life parfum - Eau de parfum voor haar - 100ml</t>
-  </si>
-  <si>
-    <t>7640158819180</t>
-  </si>
-  <si>
-    <t>Omerta Hatch Eau de Toilette 100ml</t>
-  </si>
-  <si>
-    <t>8715658997702</t>
-  </si>
-  <si>
-    <t>Omerta - Rose Pure - Eau de Parfum - 100ml</t>
-  </si>
-  <si>
-    <t>8715658380696</t>
-  </si>
-  <si>
-    <t>Real Time - Me Time - Eau de Toilette - 100Ml</t>
-  </si>
-  <si>
-    <t>8715658350705</t>
-  </si>
-  <si>
-    <t>Sentio Chalize for Woman giftset geuren 3x 15ml soorten eau de parfum</t>
-  </si>
-  <si>
-    <t>8721055492146</t>
-  </si>
-  <si>
-    <t>Dorall Everscent Eau de Toilette voor dames - 100ml</t>
-  </si>
-  <si>
-    <t>6291012875807</t>
-  </si>
-  <si>
-    <t>Creation Lamis Golden Wave Women Giftset</t>
-  </si>
-  <si>
-    <t>6291012002623</t>
-  </si>
-  <si>
-    <t>Savanna Nights - eau de toilette</t>
-  </si>
-  <si>
-    <t>6291012871038</t>
-  </si>
-  <si>
-    <t>Sentio Chalize Eau De Parfum - 100 ml</t>
-  </si>
-  <si>
-    <t>7640158815694</t>
-  </si>
-  <si>
-    <t>Street Looks Miss Important Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8715658340287</t>
-  </si>
-  <si>
-    <t>Sentio Soft Suede Eau de Parfum 100ml</t>
-  </si>
-  <si>
-    <t>8721055491453</t>
+    <t>Sentio Rose Espresso Unisex Eau de Parfum 100ml</t>
+  </si>
+  <si>
+    <t>8721055491415</t>
+  </si>
+  <si>
+    <t>Real Time - Queen Of Space Glorious - Eau De Parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658361473</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Giftset - Unicorn Dreamy Glitterwings - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055494041</t>
+  </si>
+  <si>
+    <t>Bubble Bliss - Giftset - You're Flamazing - Showergel + Eau de Parfum - Cadeauset voor Kinderen - Geschenkset</t>
+  </si>
+  <si>
+    <t>8721055494003</t>
+  </si>
+  <si>
+    <t>Omerta Express Sensualite Frivole 100ml Eau de Parfum</t>
+  </si>
+  <si>
+    <t>8715658380238</t>
+  </si>
+  <si>
+    <t>Street Looks - Fleurette - Eau de parfum - 100ML</t>
+  </si>
+  <si>
+    <t>8715658013006</t>
+  </si>
+  <si>
+    <t>Omerta - Faktz Select - Eau De Toilette - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658370215</t>
+  </si>
+  <si>
+    <t>Real Time Wild Action Eau de Toilette Spray 100ml</t>
+  </si>
+  <si>
+    <t>8715658350224</t>
+  </si>
+  <si>
+    <t>Omerta Power Boost For Men Eau de Toilette Spray 100ml</t>
+  </si>
+  <si>
+    <t>8715658370208</t>
   </si>
 </sst>
 </file>
@@ -858,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1971,19 +1863,19 @@
         <v>96</v>
       </c>
       <c r="C43" s="1">
-        <v>15.55</v>
+        <v>14.95</v>
       </c>
       <c r="D43" s="1">
-        <v>15.37</v>
+        <v>14.78</v>
       </c>
       <c r="E43" s="1">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F43" t="s">
         <v>97</v>
       </c>
       <c r="G43" s="1">
-        <v>15.37</v>
+        <v>14.78</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -2023,19 +1915,19 @@
         <v>101</v>
       </c>
       <c r="C45" s="1">
-        <v>14.95</v>
+        <v>14.19</v>
       </c>
       <c r="D45" s="1">
-        <v>14.78</v>
+        <v>14.07</v>
       </c>
       <c r="E45" s="1">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="F45" t="s">
         <v>97</v>
       </c>
       <c r="G45" s="1">
-        <v>14.78</v>
+        <v>14.07</v>
       </c>
       <c r="H45" t="s">
         <v>11</v>
@@ -2049,13 +1941,13 @@
         <v>103</v>
       </c>
       <c r="C46" s="1">
-        <v>14.95</v>
+        <v>14.89</v>
       </c>
       <c r="D46" s="1">
         <v>14.78</v>
       </c>
       <c r="E46" s="1">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="F46" t="s">
         <v>97</v>
@@ -2075,19 +1967,19 @@
         <v>105</v>
       </c>
       <c r="C47" s="1">
-        <v>14.19</v>
+        <v>14.89</v>
       </c>
       <c r="D47" s="1">
-        <v>14.07</v>
+        <v>14.78</v>
       </c>
       <c r="E47" s="1">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F47" t="s">
         <v>97</v>
       </c>
       <c r="G47" s="1">
-        <v>14.07</v>
+        <v>14.78</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -2101,19 +1993,19 @@
         <v>107</v>
       </c>
       <c r="C48" s="1">
-        <v>14.89</v>
+        <v>14.29</v>
       </c>
       <c r="D48" s="1">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="E48" s="1">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F48" t="s">
         <v>97</v>
       </c>
       <c r="G48" s="1">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -2127,19 +2019,19 @@
         <v>109</v>
       </c>
       <c r="C49" s="1">
-        <v>14.89</v>
+        <v>14.29</v>
       </c>
       <c r="D49" s="1">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="E49" s="1">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
       <c r="F49" t="s">
         <v>97</v>
       </c>
       <c r="G49" s="1">
-        <v>14.78</v>
+        <v>14.2</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -2179,19 +2071,19 @@
         <v>113</v>
       </c>
       <c r="C51" s="1">
-        <v>14.29</v>
+        <v>13.49</v>
       </c>
       <c r="D51" s="1">
-        <v>14.2</v>
+        <v>13.43</v>
       </c>
       <c r="E51" s="1">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F51" t="s">
         <v>97</v>
       </c>
       <c r="G51" s="1">
-        <v>14.2</v>
+        <v>13.43</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2205,489 +2097,21 @@
         <v>115</v>
       </c>
       <c r="C52" s="1">
-        <v>14.29</v>
+        <v>13.49</v>
       </c>
       <c r="D52" s="1">
-        <v>14.2</v>
+        <v>13.43</v>
       </c>
       <c r="E52" s="1">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="F52" t="s">
         <v>97</v>
       </c>
       <c r="G52" s="1">
-        <v>14.2</v>
+        <v>13.43</v>
       </c>
       <c r="H52" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D53" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E53" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F53" t="s">
-        <v>97</v>
-      </c>
-      <c r="G53" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H53" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>118</v>
-      </c>
-      <c r="B54" t="s">
-        <v>119</v>
-      </c>
-      <c r="C54" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D54" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E54" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F54" t="s">
-        <v>97</v>
-      </c>
-      <c r="G54" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H54" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>120</v>
-      </c>
-      <c r="B55" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D55" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E55" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F55" t="s">
-        <v>97</v>
-      </c>
-      <c r="G55" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H55" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>122</v>
-      </c>
-      <c r="B56" t="s">
-        <v>123</v>
-      </c>
-      <c r="C56" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D56" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E56" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F56" t="s">
-        <v>97</v>
-      </c>
-      <c r="G56" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H56" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" t="s">
-        <v>125</v>
-      </c>
-      <c r="C57" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D57" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E57" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F57" t="s">
-        <v>97</v>
-      </c>
-      <c r="G57" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H57" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" t="s">
-        <v>127</v>
-      </c>
-      <c r="C58" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D58" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E58" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F58" t="s">
-        <v>97</v>
-      </c>
-      <c r="G58" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H58" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>128</v>
-      </c>
-      <c r="B59" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D59" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E59" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F59" t="s">
-        <v>97</v>
-      </c>
-      <c r="G59" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H59" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" t="s">
-        <v>131</v>
-      </c>
-      <c r="C60" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D60" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E60" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F60" t="s">
-        <v>97</v>
-      </c>
-      <c r="G60" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>132</v>
-      </c>
-      <c r="B61" t="s">
-        <v>133</v>
-      </c>
-      <c r="C61" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D61" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E61" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F61" t="s">
-        <v>97</v>
-      </c>
-      <c r="G61" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" t="s">
-        <v>135</v>
-      </c>
-      <c r="C62" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D62" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E62" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H62" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>136</v>
-      </c>
-      <c r="B63" t="s">
-        <v>137</v>
-      </c>
-      <c r="C63" s="1">
-        <v>14.29</v>
-      </c>
-      <c r="D63" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="E63" s="1">
-        <v>0.09</v>
-      </c>
-      <c r="F63" t="s">
-        <v>97</v>
-      </c>
-      <c r="G63" s="1">
-        <v>14.2</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>138</v>
-      </c>
-      <c r="B64" t="s">
-        <v>139</v>
-      </c>
-      <c r="C64" s="1">
-        <v>15.59</v>
-      </c>
-      <c r="D64" s="1">
-        <v>15.51</v>
-      </c>
-      <c r="E64" s="1">
-        <v>0.08</v>
-      </c>
-      <c r="F64" t="s">
-        <v>97</v>
-      </c>
-      <c r="G64" s="1">
-        <v>15.51</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>140</v>
-      </c>
-      <c r="B65" t="s">
-        <v>141</v>
-      </c>
-      <c r="C65" s="1">
-        <v>13.89</v>
-      </c>
-      <c r="D65" s="1">
-        <v>13.82</v>
-      </c>
-      <c r="E65" s="1">
-        <v>0.07</v>
-      </c>
-      <c r="F65" t="s">
-        <v>97</v>
-      </c>
-      <c r="G65" s="1">
-        <v>13.82</v>
-      </c>
-      <c r="H65" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>142</v>
-      </c>
-      <c r="B66" t="s">
-        <v>143</v>
-      </c>
-      <c r="C66" s="1">
-        <v>13.49</v>
-      </c>
-      <c r="D66" s="1">
-        <v>13.43</v>
-      </c>
-      <c r="E66" s="1">
-        <v>0.06</v>
-      </c>
-      <c r="F66" t="s">
-        <v>97</v>
-      </c>
-      <c r="G66" s="1">
-        <v>13.43</v>
-      </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" t="s">
-        <v>145</v>
-      </c>
-      <c r="C67" s="1">
-        <v>13.75</v>
-      </c>
-      <c r="D67" s="1">
-        <v>13.7</v>
-      </c>
-      <c r="E67" s="1">
-        <v>0.05</v>
-      </c>
-      <c r="F67" t="s">
-        <v>97</v>
-      </c>
-      <c r="G67" s="1">
-        <v>13.7</v>
-      </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>146</v>
-      </c>
-      <c r="B68" t="s">
-        <v>147</v>
-      </c>
-      <c r="C68" s="1">
-        <v>12.69</v>
-      </c>
-      <c r="D68" s="1">
-        <v>12.66</v>
-      </c>
-      <c r="E68" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="F68" t="s">
-        <v>97</v>
-      </c>
-      <c r="G68" s="1">
-        <v>12.66</v>
-      </c>
-      <c r="H68" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>148</v>
-      </c>
-      <c r="B69" t="s">
-        <v>149</v>
-      </c>
-      <c r="C69" s="1">
-        <v>12.99</v>
-      </c>
-      <c r="D69" s="1">
-        <v>12.96</v>
-      </c>
-      <c r="E69" s="1">
-        <v>0.03</v>
-      </c>
-      <c r="F69" t="s">
-        <v>97</v>
-      </c>
-      <c r="G69" s="1">
-        <v>12.96</v>
-      </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>150</v>
-      </c>
-      <c r="B70" t="s">
-        <v>151</v>
-      </c>
-      <c r="C70" s="1">
-        <v>14.79</v>
-      </c>
-      <c r="D70" s="1">
-        <v>14.78</v>
-      </c>
-      <c r="E70" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="F70" t="s">
-        <v>97</v>
-      </c>
-      <c r="G70" s="1">
-        <v>14.78</v>
-      </c>
-      <c r="H70" t="s">
         <v>11</v>
       </c>
     </row>

--- a/rapporten/prijsrapport-2026-05-05.xlsx
+++ b/rapporten/prijsrapport-2026-05-05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="118">
   <si>
     <t>Product</t>
   </si>
@@ -341,6 +341,12 @@
   </si>
   <si>
     <t>8715658013006</t>
+  </si>
+  <si>
+    <t>Omerta - Invasion Third Dimension - Eau De Parfum - 100Ml</t>
+  </si>
+  <si>
+    <t>8715658380368</t>
   </si>
   <si>
     <t>Omerta - Faktz Select - Eau De Toilette - 100Ml</t>
@@ -750,7 +756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2071,19 +2077,19 @@
         <v>113</v>
       </c>
       <c r="C51" s="1">
-        <v>13.49</v>
+        <v>14.29</v>
       </c>
       <c r="D51" s="1">
-        <v>13.43</v>
+        <v>14.2</v>
       </c>
       <c r="E51" s="1">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="F51" t="s">
         <v>97</v>
       </c>
       <c r="G51" s="1">
-        <v>13.43</v>
+        <v>14.2</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2112,6 +2118,32 @@
         <v>13.43</v>
       </c>
       <c r="H52" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="1">
+        <v>13.49</v>
+      </c>
+      <c r="D53" s="1">
+        <v>13.43</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.06</v>
+      </c>
+      <c r="F53" t="s">
+        <v>97</v>
+      </c>
+      <c r="G53" s="1">
+        <v>13.43</v>
+      </c>
+      <c r="H53" t="s">
         <v>11</v>
       </c>
     </row>
